--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4188,8 +4188,60 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-13 05:30:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026/09/13 05:30:00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:15:12</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J72"/>
+  <autoFilter ref="A1:J73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4480,7 +4532,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4240,8 +4240,60 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:30:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026/09/13 10:30:00</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:38:45</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J73"/>
+  <autoFilter ref="A1:J74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4532,7 +4584,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4292,8 +4292,60 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026/09/14 00:00:05</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-13 17:19:19</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J74"/>
+  <autoFilter ref="A1:J75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4304,7 +4356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4596,156 +4648,153 @@
         <v>677.4299999999999</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>677.4299999999999</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4755,19 +4804,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4777,144 +4826,188 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-12 01:16:59</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/09/12 01:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-09-13 00:00:05</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>677.43</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/09/14 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4344,8 +4344,60 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-14 05:30:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026/09/14 05:30:00</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-13 21:38:42</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J75"/>
+  <autoFilter ref="A1:J76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4655,7 +4707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4396,8 +4396,60 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:14:15</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026/09/14 07:14:15</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:31:54</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J76"/>
+  <autoFilter ref="A1:J77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4707,7 +4759,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4448,8 +4448,60 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:33:19</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026/09/14 09:33:19</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-14 01:34:26</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J77"/>
+  <autoFilter ref="A1:J78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4759,13 +4811,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>677.4299999999999</v>
+        <v>677.3175</v>
       </c>
       <c r="D17" t="n">
-        <v>677.4299999999999</v>
+        <v>676.98</v>
       </c>
       <c r="E17" t="n">
         <v>677.4299999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4500,8 +4500,60 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:58:21</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>669.5</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>669.5</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>672.31</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>672.31</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:58:21</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:02:31</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J78"/>
+  <autoFilter ref="A1:J79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4811,10 +4863,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>677.3175</v>
+        <v>677.25</v>
       </c>
       <c r="D17" t="n">
         <v>676.98</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4552,8 +4552,60 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-14 21:53:22</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>669.85</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>669.85</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>672.67</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>672.67</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026/09/14 21:53:22</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:55:59</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
+  <autoFilter ref="A1:J80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4863,10 +4915,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>677.25</v>
+        <v>677.205</v>
       </c>
       <c r="D17" t="n">
         <v>676.98</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4604,8 +4604,60 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:49:50</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026/09/15 02:49:50</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:06:05</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J80"/>
+  <autoFilter ref="A1:J81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4616,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4927,156 +4979,153 @@
         <v>677.4299999999999</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>676.98</v>
+      </c>
+      <c r="D18" t="n">
+        <v>676.98</v>
+      </c>
+      <c r="E18" t="n">
+        <v>676.98</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5086,19 +5135,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5108,129 +5157,129 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5240,34 +5289,78 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-13 00:00:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/09/13 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2026-09-14 00:00:05</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>677.43</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:49:50</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/09/15 02:49:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4656,8 +4656,60 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:30:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026/09/15 05:30:00</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:27:22</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J81"/>
+  <autoFilter ref="A1:J82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4986,7 +5038,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>676.98</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4708,8 +4708,60 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:27:11</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026/09/15 08:27:11</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:50:31</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5038,7 +5090,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>676.98</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4760,8 +4760,60 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:28:26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>672.7</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>672.7</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026/09/15 13:28:26</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:33:00</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5090,13 +5142,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>676.98</v>
+        <v>676.91</v>
       </c>
       <c r="D18" t="n">
-        <v>676.98</v>
+        <v>676.7</v>
       </c>
       <c r="E18" t="n">
         <v>676.98</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4812,8 +4812,60 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:18:27</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>669.98</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>669.98</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>672.8</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>672.8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026/09/15 18:18:27</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:24:00</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J84"/>
+  <autoFilter ref="A1:J85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5142,10 +5194,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>676.91</v>
+        <v>676.8680000000001</v>
       </c>
       <c r="D18" t="n">
         <v>676.7</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4864,8 +4864,60 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:03:37</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>669.99</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>669.99</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>672.81</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>672.81</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026/09/15 23:03:37</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:09:37</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J85"/>
+  <autoFilter ref="A1:J86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5194,10 +5246,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>676.8680000000001</v>
+        <v>676.84</v>
       </c>
       <c r="D18" t="n">
         <v>676.7</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4916,8 +4916,60 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:49:33</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026/09/16 02:49:33</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:00:36</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4928,7 +4980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5258,156 +5310,153 @@
         <v>676.98</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>676.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>676.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>676.7</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5417,19 +5466,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5439,129 +5488,129 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5571,19 +5620,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5593,34 +5642,78 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>677.43</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/09/14 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-09-15 02:49:50</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>676.98</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:49:33</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/09/16 02:49:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4968,8 +4968,60 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-16 05:30:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026/09/16 05:30:00</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:07:02</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J87"/>
+  <autoFilter ref="A1:J88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5317,7 +5369,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>676.7</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5020,8 +5020,60 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-16 06:40:29</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>670.07</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>672.89</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:40:29</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:16:17</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J88"/>
+  <autoFilter ref="A1:J89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5369,7 +5421,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>676.7</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5072,8 +5072,60 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:54:07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>669.79</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>669.79</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>672.61</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>672.61</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026/09/16 12:54:07</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:57:40</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5421,13 +5473,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>676.7</v>
+        <v>676.595</v>
       </c>
       <c r="D19" t="n">
-        <v>676.7</v>
+        <v>676.28</v>
       </c>
       <c r="E19" t="n">
         <v>676.7</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5124,8 +5124,60 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:43:33</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>672.36</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>672.36</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026/09/16 17:43:33</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:49:19</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5473,10 +5525,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>676.595</v>
+        <v>676.532</v>
       </c>
       <c r="D19" t="n">
         <v>676.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5176,8 +5176,60 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:13:34</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026/09/16 22:13:34</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:23:30</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5525,10 +5577,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>676.532</v>
+        <v>676.49</v>
       </c>
       <c r="D19" t="n">
         <v>676.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5228,8 +5228,60 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:15:47</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>669.57</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>672.38</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026/09/17 02:15:47</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-16 18:17:07</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5240,7 +5292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5589,156 +5641,153 @@
         <v>676.7</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>676.28</v>
+      </c>
+      <c r="D20" t="n">
+        <v>676.28</v>
+      </c>
+      <c r="E20" t="n">
+        <v>676.28</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5748,19 +5797,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5770,129 +5819,129 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5902,19 +5951,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5924,56 +5973,100 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:49:50</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>676.98</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/09/15 02:49:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-09-16 02:49:33</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>676.7</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:15:47</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/09/17 02:15:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5280,8 +5280,60 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:54:34</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026/09/17 02:54:34</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:25:30</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5648,7 +5700,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>676.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5332,8 +5332,60 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:41:58</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>669.8</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>672.62</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026/09/17 07:41:58</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:44:12</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5700,7 +5752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>676.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5384,8 +5384,60 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:43:37</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>670.09</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>670.09</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>672.91</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>672.91</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026/09/17 09:43:37</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:45:28</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5752,13 +5804,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>676.28</v>
+        <v>676.16</v>
       </c>
       <c r="D20" t="n">
-        <v>676.28</v>
+        <v>675.8</v>
       </c>
       <c r="E20" t="n">
         <v>676.28</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5436,8 +5436,60 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:43:38</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>669.62</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>669.62</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>672.43</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>672.43</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026/09/17 14:43:38</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-17 06:44:59</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5804,10 +5856,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>676.16</v>
+        <v>676.088</v>
       </c>
       <c r="D20" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5488,8 +5488,60 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:08:39</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026/09/17 20:08:39</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:11:33</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5856,10 +5908,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>676.088</v>
+        <v>676.04</v>
       </c>
       <c r="D20" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5540,8 +5540,60 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:58:41</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>669.51</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>669.51</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>672.32</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>672.32</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026/09/18 00:58:41</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:01:37</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5552,7 +5604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5920,156 +5972,153 @@
         <v>676.28</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>675.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>675.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>675.8</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6079,19 +6128,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6101,129 +6150,129 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6233,19 +6282,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6255,78 +6304,122 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:49:33</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>676.7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/09/16 02:49:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-09-17 02:15:47</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>676.28</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:58:41</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/09/18 00:58:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5592,8 +5592,60 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:49:21</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026/09/18 02:49:21</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:13:31</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5979,7 +6031,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5644,8 +5644,60 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-18 06:40:33</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026/09/18 06:40:33</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-17 22:52:20</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6031,7 +6083,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5696,8 +5696,60 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-09-18 08:31:09</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>669.61</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>672.42</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026/09/18 08:31:09</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:56:27</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6083,7 +6135,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5748,8 +5748,60 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:38:44</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>668.74</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>668.74</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>671.55</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>671.55</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026/09/18 13:38:44</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:41:18</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6135,13 +6187,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>675.8</v>
+        <v>675.682</v>
       </c>
       <c r="D21" t="n">
-        <v>675.8</v>
+        <v>675.21</v>
       </c>
       <c r="E21" t="n">
         <v>675.8</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5800,8 +5800,60 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:58:45</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>668.68</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>668.68</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>671.49</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>671.49</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026/09/18 17:58:45</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:03:18</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:J104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6187,10 +6239,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>675.682</v>
+        <v>675.6033</v>
       </c>
       <c r="D21" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5852,8 +5852,60 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:23:46</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>668.84</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>668.84</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026/09/18 22:23:46</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:26:21</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6239,10 +6291,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>675.6033</v>
+        <v>675.5471</v>
       </c>
       <c r="D21" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5904,8 +5904,60 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:43:47</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>671.54</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>671.54</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026/09/19 01:43:47</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:47:47</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5916,7 +5968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6303,156 +6355,153 @@
         <v>675.8</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="D22" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>675.21</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6462,19 +6511,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6484,129 +6533,129 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6616,19 +6665,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6638,100 +6687,144 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:15:47</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>676.28</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/09/17 02:15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2026-09-18 00:58:41</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>675.8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:43:47</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/09/19 01:43:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5956,8 +5956,60 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-09-19 02:49:22</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026/09/19 02:49:22</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:00:42</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6362,7 +6414,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6008,8 +6008,60 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:30:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026/09/19 05:30:00</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:30:49</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J107"/>
+  <autoFilter ref="A1:J108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6414,7 +6466,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6060,8 +6060,60 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-09-19 10:30:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026/09/19 10:30:00</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00:08</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J108"/>
+  <autoFilter ref="A1:J109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6466,7 +6518,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6112,8 +6112,60 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:00:05</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026/09/20 00:00:05</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:33:13</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J109"/>
+  <autoFilter ref="A1:J110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6124,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6530,156 +6582,153 @@
         <v>675.21</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="D23" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="E23" t="n">
+        <v>675.21</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6689,19 +6738,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6711,129 +6760,129 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6843,19 +6892,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6865,122 +6914,166 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:58:41</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>675.8</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/09/18 00:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-09-19 01:43:47</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>675.21</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:00:05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/09/20 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6164,8 +6164,60 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-09-20 05:30:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026/09/20 05:30:00</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:04:38</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6589,7 +6641,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6216,8 +6216,60 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:30:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026/09/20 10:30:00</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-20 06:07:59</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
+  <autoFilter ref="A1:J112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6641,7 +6693,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6268,8 +6268,60 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:05</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026/09/21 00:00:05</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:42:24</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6280,7 +6332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6705,156 +6757,153 @@
         <v>675.21</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>675.21</v>
+      </c>
+      <c r="E24" t="n">
+        <v>675.21</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6864,19 +6913,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6886,129 +6935,129 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7018,19 +7067,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7040,144 +7089,188 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:43:47</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/09/19 01:43:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-09-20 00:00:05</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>675.21</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/09/21 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6320,8 +6320,60 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-09-21 05:30:00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026/09/21 05:30:00</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-20 21:55:29</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J113"/>
+  <autoFilter ref="A1:J114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6764,7 +6816,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6372,8 +6372,60 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:28:13</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>668.83</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>671.64</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026/09/21 07:28:13</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-20 23:55:23</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
+  <autoFilter ref="A1:J115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6816,7 +6868,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6424,8 +6424,60 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:45:15</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>668.42</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>668.42</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>671.23</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>671.23</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026/09/21 11:45:15</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-21 03:52:24</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
+  <autoFilter ref="A1:J116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6868,13 +6920,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>675.21</v>
+        <v>675.125</v>
       </c>
       <c r="D24" t="n">
-        <v>675.21</v>
+        <v>674.87</v>
       </c>
       <c r="E24" t="n">
         <v>675.21</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6476,8 +6476,60 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:25:16</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>668.4</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>668.4</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>671.21</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>671.21</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026/09/21 17:25:16</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:29:38</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J116"/>
+  <autoFilter ref="A1:J117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6920,10 +6972,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>675.125</v>
+        <v>675.074</v>
       </c>
       <c r="D24" t="n">
         <v>674.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6528,8 +6528,60 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:55:17</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>668.35</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>668.35</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>671.16</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>671.16</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026/09/21 23:55:17</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:59:39</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J117"/>
+  <autoFilter ref="A1:J118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6972,10 +7024,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>675.074</v>
+        <v>675.04</v>
       </c>
       <c r="D24" t="n">
         <v>674.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6580,8 +6580,60 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-09-22 02:54:30</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>668.45</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>668.45</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>671.26</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>671.26</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026/09/22 02:54:30</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-21 20:23:10</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6592,7 +6644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7036,156 +7088,153 @@
         <v>675.21</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>674.87</v>
+      </c>
+      <c r="D25" t="n">
+        <v>674.87</v>
+      </c>
+      <c r="E25" t="n">
+        <v>674.87</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7195,19 +7244,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7217,129 +7266,129 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7349,19 +7398,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7371,129 +7420,129 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7503,34 +7552,78 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:00:05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/09/20 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>2026-09-21 00:00:05</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>675.21</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-22 02:54:30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/09/22 02:54:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6632,8 +6632,60 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-09-22 06:40:19</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>668.45</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>668.45</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>671.26</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>671.26</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026/09/22 06:40:19</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:27:23</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
+  <autoFilter ref="A1:J120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7095,7 +7147,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>674.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6684,8 +6684,60 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:40:20</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>668.4</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>668.4</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>671.21</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>671.21</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026/09/22 09:40:20</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-22 01:45:42</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J120"/>
+  <autoFilter ref="A1:J121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7147,13 +7199,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>674.87</v>
+        <v>674.7767</v>
       </c>
       <c r="D25" t="n">
-        <v>674.87</v>
+        <v>674.59</v>
       </c>
       <c r="E25" t="n">
         <v>674.87</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6736,8 +6736,60 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:49:11</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>668.69</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>668.69</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>671.5</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>671.5</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:49:11</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-09-22 06:50:35</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7199,10 +7251,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>674.7767</v>
+        <v>674.73</v>
       </c>
       <c r="D25" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6788,8 +6788,60 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-09-22 20:05:22</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>668.84</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>668.84</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026/09/22 20:05:22</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:11:15</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:J123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7251,10 +7303,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>674.73</v>
+        <v>674.702</v>
       </c>
       <c r="D25" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6840,8 +6840,60 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:05</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>668.81</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>668.81</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026/09/23 00:00:05</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:58:46</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J123"/>
+  <autoFilter ref="A1:J124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6852,7 +6904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7315,156 +7367,153 @@
         <v>674.87</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>674.59</v>
+      </c>
+      <c r="D26" t="n">
+        <v>674.59</v>
+      </c>
+      <c r="E26" t="n">
+        <v>674.59</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7474,19 +7523,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7496,129 +7545,129 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7628,19 +7677,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7650,129 +7699,129 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7782,19 +7831,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7804,34 +7853,78 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:05</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>675.21</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/09/21 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2026-09-22 02:54:30</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>674.87</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/09/23 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6892,8 +6892,60 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-09-23 02:56:04</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>668.97</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>668.97</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>671.78</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>671.78</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026/09/23 02:56:04</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-22 20:05:59</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J124"/>
+  <autoFilter ref="A1:J125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7374,7 +7426,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6944,8 +6944,60 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:43:42</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>668.97</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>668.97</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>671.78</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>671.78</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026/09/23 06:43:42</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-09-22 22:54:51</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J125"/>
+  <autoFilter ref="A1:J126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7426,7 +7478,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6996,8 +6996,60 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15:43</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>669.12</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>669.12</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>671.93</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>671.93</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026/09/23 09:15:43</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:16:24</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J126"/>
+  <autoFilter ref="A1:J127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7478,16 +7530,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>674.59</v>
+        <v>674.6125</v>
       </c>
       <c r="D26" t="n">
         <v>674.59</v>
       </c>
       <c r="E26" t="n">
-        <v>674.59</v>
+        <v>674.6799999999999</v>
       </c>
     </row>
     <row r="27"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7048,8 +7048,60 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:00:27</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026/09/23 14:00:27</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:04:59</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J127"/>
+  <autoFilter ref="A1:J128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7530,10 +7582,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>674.6125</v>
+        <v>674.626</v>
       </c>
       <c r="D26" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7100,8 +7100,60 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:25:28</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>669.7</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>669.7</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>672.51</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>672.51</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026/09/23 19:25:28</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:28:17</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
+  <autoFilter ref="A1:J129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7582,10 +7634,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>674.626</v>
+        <v>674.635</v>
       </c>
       <c r="D26" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7152,8 +7152,60 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:30:29</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>670.11</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>670.11</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>672.93</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>672.93</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026/09/23 23:30:29</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:32:24</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J129"/>
+  <autoFilter ref="A1:J130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7634,10 +7686,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>674.635</v>
+        <v>674.6414</v>
       </c>
       <c r="D26" t="n">
         <v>674.59</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$130</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7204,8 +7204,60 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:55:59</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026/09/24 02:55:59</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:11:40</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J130"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7216,7 +7268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7698,156 +7750,153 @@
         <v>674.6799999999999</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>674.6799999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>674.6799999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>674.6799999999999</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7857,19 +7906,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7879,129 +7928,129 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8011,19 +8060,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8033,129 +8082,129 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8165,19 +8214,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8187,56 +8236,100 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-22 02:54:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>674.87</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/09/22 02:54:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>2026-09-23 00:00:05</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>674.59</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:55:59</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/09/24 02:55:59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
+  <autoFilter ref="A1:E27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7256,8 +7256,60 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:30:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026/09/24 05:30:00</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:18:26</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7757,7 +7809,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>674.6799999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7308,8 +7308,60 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:48</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>670.19</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>673.01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026/09/24 07:53:48</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:35:55</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7809,7 +7861,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>674.6799999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$134</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7360,8 +7360,60 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:10:32</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>670.38</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>670.38</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>673.2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>673.2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:10:32</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:22:47</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7861,16 +7913,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>674.6799999999999</v>
+        <v>674.7325</v>
       </c>
       <c r="D27" t="n">
         <v>674.6799999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>674.6799999999999</v>
+        <v>674.89</v>
       </c>
     </row>
     <row r="28"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7412,8 +7412,60 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:15:33</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>670.3</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>670.3</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>673.12</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>673.12</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026/09/24 18:15:33</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:18:36</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J134"/>
+  <autoFilter ref="A1:J135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7913,10 +7965,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>674.7325</v>
+        <v>674.764</v>
       </c>
       <c r="D27" t="n">
         <v>674.6799999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7464,8 +7464,60 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:15:34</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>670.26</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>670.26</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>673.08</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>673.08</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026/09/24 23:15:34</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:16:17</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J135"/>
+  <autoFilter ref="A1:J136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7965,10 +8017,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>674.764</v>
+        <v>674.785</v>
       </c>
       <c r="D27" t="n">
         <v>674.6799999999999</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7516,8 +7516,60 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:51:04</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026/09/25 02:51:04</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-09-24 19:17:24</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J136"/>
+  <autoFilter ref="A1:J137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7528,7 +7580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8029,156 +8081,153 @@
         <v>674.89</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="D28" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="E28" t="n">
+        <v>674.89</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8188,19 +8237,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8210,129 +8259,129 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8342,19 +8391,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8364,129 +8413,129 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8496,19 +8545,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8518,78 +8567,122 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>674.59</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/09/23 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>2026-09-24 02:55:59</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>674.68</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2026/09/24 02:55:59</t>
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:51:04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/09/25 02:51:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E27"/>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7568,8 +7568,60 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:30:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026/09/25 05:30:00</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:32:12</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J137"/>
+  <autoFilter ref="A1:J138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8088,7 +8140,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7620,8 +7620,60 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:46:46</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026/09/25 06:46:46</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-09-25 00:45:20</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J138"/>
+  <autoFilter ref="A1:J139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8140,7 +8192,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7672,8 +7672,60 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:25:38</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026/09/25 13:25:38</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:28:05</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J139"/>
+  <autoFilter ref="A1:J140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8192,7 +8244,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7724,8 +7724,60 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:25:39</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026/09/25 18:25:39</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:28:44</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J140"/>
+  <autoFilter ref="A1:J141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8244,7 +8296,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7776,8 +7776,60 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-09-25 22:51:11</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026/09/25 22:51:11</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:28:55</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J141"/>
+  <autoFilter ref="A1:J142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8296,7 +8348,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7828,8 +7828,60 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026/09/26 00:00:05</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-09-25 19:28:10</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J142"/>
+  <autoFilter ref="A1:J143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7840,7 +7892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8360,156 +8412,153 @@
         <v>674.89</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="D29" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="E29" t="n">
+        <v>674.89</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8519,19 +8568,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8541,129 +8590,129 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8673,19 +8722,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8695,129 +8744,129 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8827,19 +8876,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8849,100 +8898,144 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-24 02:55:59</t>
+          <t>2026-09-23 00:00:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>674.68</t>
+          <t>674.59</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/09/24 02:55:59</t>
+          <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:55:59</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>674.68</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/09/24 02:55:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>2026-09-25 02:51:04</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>674.89</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2026/09/25 02:51:04</t>
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/09/26 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7880,8 +7880,60 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-09-26 05:30:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026/09/26 05:30:00</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-09-25 22:42:55</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J143"/>
+  <autoFilter ref="A1:J144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8419,7 +8471,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7932,8 +7932,60 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:30:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026/09/26 10:30:00</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-26 05:55:22</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8471,7 +8523,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7984,8 +7984,60 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:00:05</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026/09/27 00:00:05</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:26:30</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J145"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7996,7 +8048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8535,156 +8587,153 @@
         <v>674.89</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="D30" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="E30" t="n">
+        <v>674.89</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8694,19 +8743,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8716,129 +8765,129 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8848,19 +8897,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8870,129 +8919,129 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9002,19 +9051,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9024,122 +9073,166 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-24 02:55:59</t>
+          <t>2026-09-23 00:00:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>674.68</t>
+          <t>674.59</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/09/24 02:55:59</t>
+          <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-25 02:51:04</t>
+          <t>2026-09-24 02:55:59</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>674.89</t>
+          <t>674.68</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/09/25 02:51:04</t>
+          <t>2026/09/24 02:55:59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:51:04</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/09/25 02:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>2026-09-26 00:00:05</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>674.89</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>2026/09/26 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:00:05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026/09/27 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E29"/>
+  <autoFilter ref="A1:E30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J146"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8036,8 +8036,60 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:30:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026/09/27 05:30:00</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:44:34</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J146"/>
+  <autoFilter ref="A1:J147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8594,7 +8646,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8088,8 +8088,60 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-09-27 10:30:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026/09/27 10:30:00</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-27 07:29:03</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J147"/>
+  <autoFilter ref="A1:J148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8646,7 +8698,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8140,8 +8140,60 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00:05</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026/09/28 00:00:05</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-27 17:48:17</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J148"/>
+  <autoFilter ref="A1:J149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8152,7 +8204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8710,156 +8762,153 @@
         <v>674.89</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="D31" t="n">
+        <v>674.89</v>
+      </c>
+      <c r="E31" t="n">
+        <v>674.89</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8869,19 +8918,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8891,129 +8940,129 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9023,19 +9072,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9045,129 +9094,129 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9177,19 +9226,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9199,107 +9248,107 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-24 02:55:59</t>
+          <t>2026-09-23 00:00:05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>674.68</t>
+          <t>674.59</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/09/24 02:55:59</t>
+          <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-25 02:51:04</t>
+          <t>2026-09-24 02:55:59</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>674.89</t>
+          <t>674.68</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/09/25 02:51:04</t>
+          <t>2026/09/24 02:55:59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-26 00:00:05</t>
+          <t>2026-09-25 02:51:04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9309,34 +9358,78 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/09/26 00:00:05</t>
+          <t>2026/09/25 02:51:04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026/09/26 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>2026-09-27 00:00:05</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>674.89</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>2026/09/27 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00:05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026/09/28 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8192,8 +8192,60 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:06:26</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026/09/28 07:06:26</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:20:00</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J149"/>
+  <autoFilter ref="A1:J150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8769,7 +8821,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8244,8 +8244,60 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:45:54</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>670.44</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>670.44</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>673.26</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>673.26</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>673.99</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026/09/28 09:45:54</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:47:05</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J150"/>
+  <autoFilter ref="A1:J151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8821,13 +8873,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>674.89</v>
+        <v>674.59</v>
       </c>
       <c r="D31" t="n">
-        <v>674.89</v>
+        <v>673.99</v>
       </c>
       <c r="E31" t="n">
         <v>674.89</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8296,8 +8296,60 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:40:56</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>673.02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>673.99</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026/09/28 15:40:56</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:45:04</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J151"/>
+  <autoFilter ref="A1:J152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8873,10 +8925,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>674.59</v>
+        <v>674.4400000000001</v>
       </c>
       <c r="D31" t="n">
         <v>673.99</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$152</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8348,8 +8348,60 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:00:58</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>669.93</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>669.93</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>672.75</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>672.75</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>673.99</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026/09/29 00:00:58</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:04:03</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J152"/>
+  <autoFilter ref="A1:J153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8360,7 +8412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8937,156 +8989,153 @@
         <v>674.89</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>673.99</v>
+      </c>
+      <c r="D32" t="n">
+        <v>673.99</v>
+      </c>
+      <c r="E32" t="n">
+        <v>673.99</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9096,19 +9145,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9118,129 +9167,129 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9250,19 +9299,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9272,129 +9321,129 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9404,19 +9453,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9426,107 +9475,107 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-24 02:55:59</t>
+          <t>2026-09-23 00:00:05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>674.68</t>
+          <t>674.59</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/09/24 02:55:59</t>
+          <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-25 02:51:04</t>
+          <t>2026-09-24 02:55:59</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>674.89</t>
+          <t>674.68</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/09/25 02:51:04</t>
+          <t>2026/09/24 02:55:59</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-26 00:00:05</t>
+          <t>2026-09-25 02:51:04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9536,19 +9585,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/09/26 00:00:05</t>
+          <t>2026/09/25 02:51:04</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-27 00:00:05</t>
+          <t>2026-09-26 00:00:05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9558,34 +9607,78 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/09/27 00:00:05</t>
+          <t>2026/09/26 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:00:05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026/09/27 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>2026-09-28 00:00:05</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>674.89</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2026/09/28 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:00:58</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>673.99</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026/09/29 00:00:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8400,8 +8400,60 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:30:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>670.02</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>670.02</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>672.84</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>672.84</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>673.99</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026/09/29 05:30:00</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:54:27</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J153"/>
+  <autoFilter ref="A1:J154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8996,7 +9048,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>673.99</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8452,8 +8452,60 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15:37</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>670.37</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>673.19</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026/09/29 09:15:37</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:29:06</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J154"/>
+  <autoFilter ref="A1:J155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9048,16 +9100,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>673.99</v>
+        <v>674.03</v>
       </c>
       <c r="D32" t="n">
         <v>673.99</v>
       </c>
       <c r="E32" t="n">
-        <v>673.99</v>
+        <v>674.11</v>
       </c>
     </row>
     <row r="33"/>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8504,8 +8504,60 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:26:01</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>669.53</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>672.34</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026/09/29 15:26:01</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:26:45</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J155"/>
+  <autoFilter ref="A1:J156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9100,10 +9152,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>674.03</v>
+        <v>674.05</v>
       </c>
       <c r="D32" t="n">
         <v>673.99</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8556,8 +8556,60 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:11:03</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>669.68</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>669.68</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026/09/29 22:11:03</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:15:33</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J156"/>
+  <autoFilter ref="A1:J157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9152,10 +9204,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>674.05</v>
+        <v>674.062</v>
       </c>
       <c r="D32" t="n">
         <v>673.99</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$157</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8608,8 +8608,60 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-09-30 02:46:12</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026/09/30 02:46:12</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-09-29 19:27:55</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J157"/>
+  <autoFilter ref="A1:J158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8620,7 +8672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9216,156 +9268,153 @@
         <v>674.11</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>674.11</v>
+      </c>
+      <c r="D33" t="n">
+        <v>674.11</v>
+      </c>
+      <c r="E33" t="n">
+        <v>674.11</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 02:50:03</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>678.28</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/09/01 02:50:03</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:02</t>
+          <t>2026-09-01 02:50:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>678.09</t>
+          <t>678.28</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/09/02 00:56:02</t>
+          <t>2026/09/01 02:50:03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:16:07</t>
+          <t>2026-09-02 00:56:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>678.29</t>
+          <t>678.09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/09/03 01:16:07</t>
+          <t>2026/09/02 00:56:02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-04 01:11:13</t>
+          <t>2026-09-03 01:16:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>678.07</t>
+          <t>678.29</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:13</t>
+          <t>2026/09/03 01:16:07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-05 00:51:19</t>
+          <t>2026-09-04 01:11:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>677.87</t>
+          <t>678.07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/09/05 00:51:19</t>
+          <t>2026/09/04 01:11:13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-06 00:00:05</t>
+          <t>2026-09-05 00:51:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9375,19 +9424,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/09/06 00:00:05</t>
+          <t>2026/09/05 00:51:19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 00:00:05</t>
+          <t>2026-09-06 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9397,129 +9446,129 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/09/07 00:00:05</t>
+          <t>2026/09/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-08 02:50:02</t>
+          <t>2026-09-07 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>677.95</t>
+          <t>677.87</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/09/08 02:50:02</t>
+          <t>2026/09/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:41:42</t>
+          <t>2026-09-08 02:50:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>678.04</t>
+          <t>677.95</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/09/09 01:41:42</t>
+          <t>2026/09/08 02:50:02</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-10 01:46:48</t>
+          <t>2026-09-09 01:41:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>677.69</t>
+          <t>678.04</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/09/10 01:46:48</t>
+          <t>2026/09/09 01:41:42</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-11 01:21:54</t>
+          <t>2026-09-10 01:46:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>677.66</t>
+          <t>677.69</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/09/11 01:21:54</t>
+          <t>2026/09/10 01:46:48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-12 01:16:59</t>
+          <t>2026-09-11 01:21:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>677.43</t>
+          <t>677.66</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/09/12 01:16:59</t>
+          <t>2026/09/11 01:21:54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:05</t>
+          <t>2026-09-12 01:16:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9529,19 +9578,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/09/13 00:00:05</t>
+          <t>2026/09/12 01:16:59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:05</t>
+          <t>2026-09-13 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9551,129 +9600,129 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/09/14 00:00:05</t>
+          <t>2026/09/13 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 02:49:50</t>
+          <t>2026-09-14 00:00:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>676.98</t>
+          <t>677.43</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/09/15 02:49:50</t>
+          <t>2026/09/14 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-16 02:49:33</t>
+          <t>2026-09-15 02:49:50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>676.7</t>
+          <t>676.98</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/09/16 02:49:33</t>
+          <t>2026/09/15 02:49:50</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-17 02:15:47</t>
+          <t>2026-09-16 02:49:33</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>676.28</t>
+          <t>676.7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/09/17 02:15:47</t>
+          <t>2026/09/16 02:49:33</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-18 00:58:41</t>
+          <t>2026-09-17 02:15:47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>675.8</t>
+          <t>676.28</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/09/18 00:58:41</t>
+          <t>2026/09/17 02:15:47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-19 01:43:47</t>
+          <t>2026-09-18 00:58:41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>675.21</t>
+          <t>675.8</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/09/19 01:43:47</t>
+          <t>2026/09/18 00:58:41</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-20 00:00:05</t>
+          <t>2026-09-19 01:43:47</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9683,19 +9732,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/09/20 00:00:05</t>
+          <t>2026/09/19 01:43:47</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-21 00:00:05</t>
+          <t>2026-09-20 00:00:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9705,107 +9754,107 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/09/21 00:00:05</t>
+          <t>2026/09/20 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-22 02:54:30</t>
+          <t>2026-09-21 00:00:05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>674.87</t>
+          <t>675.21</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/09/22 02:54:30</t>
+          <t>2026/09/21 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-23 00:00:05</t>
+          <t>2026-09-22 02:54:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>674.59</t>
+          <t>674.87</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/09/23 00:00:05</t>
+          <t>2026/09/22 02:54:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-24 02:55:59</t>
+          <t>2026-09-23 00:00:05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>674.68</t>
+          <t>674.59</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/09/24 02:55:59</t>
+          <t>2026/09/23 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-25 02:51:04</t>
+          <t>2026-09-24 02:55:59</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>674.89</t>
+          <t>674.68</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/09/25 02:51:04</t>
+          <t>2026/09/24 02:55:59</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-26 00:00:05</t>
+          <t>2026-09-25 02:51:04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9815,19 +9864,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/09/26 00:00:05</t>
+          <t>2026/09/25 02:51:04</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-27 00:00:05</t>
+          <t>2026-09-26 00:00:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9837,19 +9886,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/09/27 00:00:05</t>
+          <t>2026/09/26 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-28 00:00:05</t>
+          <t>2026-09-27 00:00:05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9859,34 +9908,78 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/09/28 00:00:05</t>
+          <t>2026/09/27 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00:05</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>674.89</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026/09/28 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2026-09-29 00:00:58</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>673.99</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>2026/09/29 00:00:58</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-30 02:46:12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026/09/30 02:46:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8660,8 +8660,60 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:38:21</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>674.11</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026/09/30 06:38:21</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:07:55</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J158"/>
+  <autoFilter ref="A1:J159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9275,7 +9327,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>674.11</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8712,8 +8712,60 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:01:06</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>669.64</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>669.64</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>672.45</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>672.45</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026/09/30 10:01:06</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-09-30 02:06:07</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J159"/>
+  <autoFilter ref="A1:J160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9327,13 +9379,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>674.11</v>
+        <v>673.91</v>
       </c>
       <c r="D33" t="n">
-        <v>674.11</v>
+        <v>673.51</v>
       </c>
       <c r="E33" t="n">
         <v>674.11</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8764,8 +8764,60 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:21:07</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>669.71</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>669.71</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>672.52</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>672.52</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026/09/30 16:21:07</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:28:05</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J160"/>
+  <autoFilter ref="A1:J161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9379,10 +9431,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>673.91</v>
+        <v>673.8099999999999</v>
       </c>
       <c r="D33" t="n">
         <v>673.51</v>

--- a/data/2026/2026-09.xlsx
+++ b/data/2026/2026-09.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8816,8 +8816,60 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:11:09</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>669.74</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>672.55</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026/09/30 23:11:09</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:12:10</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J161"/>
+  <autoFilter ref="A1:J162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9431,10 +9483,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>673.8099999999999</v>
+        <v>673.75</v>
       </c>
       <c r="D33" t="n">
         <v>673.51</v>
